--- a/Part2_Create_test/Valid_cases.xlsx
+++ b/Part2_Create_test/Valid_cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\personal_webpage\my-portfolio\APR_code_gen\Part2_Create_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8A69AFD-7C5E-49C6-94A4-366486FB96C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C6CBD5-E3AA-4067-B677-794F3BDDA73F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="18735" windowHeight="15345" xr2:uid="{92CE2E25-D304-4267-9B0B-50D70ED2F8AA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{92CE2E25-D304-4267-9B0B-50D70ED2F8AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,9 +35,80 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="22">
+  <si>
+    <t>reproduced</t>
+  </si>
+  <si>
+    <t>0.45.0, 0.45.1, 0.45.2, 0.45.3, 0.46.0, 0.46.1, 0.46.2, 0.46.3</t>
+  </si>
+  <si>
+    <t>0.45.0, 0.45.1, 0.45.2, 0.45.3, 0.46.0, 0.46.1, 0.46.2, 0.46.3, 1.0.0, 1.0.1, 1.0.2, 1.1.0, 1.1.1, 1.1.2, 1.2.0, 1.2.1, 1.2.2, 1.2.4, 2.0.0, 2.2.0, 2.3.0, 2.4.0, 2.5.0</t>
+  </si>
+  <si>
+    <t>1.0.0, 1.0.1, 1.0.2, 1.1.0, 1.1.1, 1.1.2, 1.2.0, 1.2.1, 1.2.2, 1.2.4, 2.0.0, 2.2.0, 2.3.0, 2.4.0, 2.5.0</t>
+  </si>
+  <si>
+    <t>0.25.0, 0.25.1, 0.25.2, 0.25.3, 0.45.0, 0.45.1, 0.45.2, 0.45.3, 0.46.0, 0.46.1, 0.46.2, 0.46.3, 1.0.0, 1.0.1, 1.0.2, 1.1.0, 1.1.1, 1.1.2, 1.2.0, 1.2.1, 1.2.2, 1.2.4, 2.0.0, 2.2.0, 2.3.0, 2.4.0, 2.5.0</t>
+  </si>
+  <si>
+    <t>0.25.0, 0.25.1, 0.25.2, 0.25.3, 0.45.0, 0.45.1, 0.45.2, 0.45.3, 0.46.0, 0.46.1, 0.46.2, 0.46.3</t>
+  </si>
+  <si>
+    <t>0.25.0, 0.25.1, 0.25.2, 0.25.3, 0.45.0, 0.45.1, 0.45.2, 0.45.3, 0.46.0, 0.46.1, 0.46.2, 0.46.3, 1.0.0, 1.0.1, 1.0.2</t>
+  </si>
+  <si>
+    <t>0.25.0, 0.25.1, 0.25.2, 0.25.3</t>
+  </si>
+  <si>
+    <t>1.0.0, 1.0.1, 1.0.2, 1.1.0, 1.1.1, 1.1.2, 1.2.0, 1.2.1, 1.2.2, 1.2.4</t>
+  </si>
+  <si>
+    <t>0.25.0, 0.25.1, 0.25.2, 0.25.3, 0.45.0, 0.45.1, 0.45.2, 0.45.3</t>
+  </si>
+  <si>
+    <t>1.2.0, 1.2.1, 1.2.2, 1.2.4, 2.0.0, 2.2.0, 2.3.0, 2.4.0</t>
+  </si>
+  <si>
+    <t>1.1.0, 1.1.1, 1.1.2, 1.2.0, 1.2.1, 1.2.2, 1.2.4, 2.0.0, 2.2.0, 2.3.0, 2.4.0, 2.5.0</t>
+  </si>
+  <si>
+    <t>1.2.0, 1.2.1, 1.2.2, 1.2.4, 2.0.0, 2.2.0, 2.3.0, 2.4.0, 2.5.0</t>
+  </si>
+  <si>
+    <t>0.45.0, 0.45.1, 0.45.2, 0.45.3, 0.46.0, 0.46.1, 0.46.2, 0.46.3, 1.0.0, 1.0.1, 1.0.2, 1.1.0, 1.1.1, 1.1.2, 1.2.0, 1.2.1, 1.2.2, 1.2.4, 2.0.0, 2.5.0</t>
+  </si>
+  <si>
+    <t>0.46.0, 0.46.1, 0.46.2, 0.46.3, 1.0.0, 1.0.1, 1.0.2, 1.1.0, 1.1.1, 1.1.2, 1.2.0, 1.2.1, 1.2.2, 1.2.4, 2.0.0, 2.2.0, 2.3.0, 2.4.0, 2.5.0</t>
+  </si>
+  <si>
+    <t>0.45.0, 0.45.1, 0.45.2, 0.45.3, 0.46.0, 0.46.1, 0.46.2, 0.46.3, 1.0.0, 1.0.1, 1.0.2, 1.1.0, 1.1.1, 1.1.2, 1.2.0, 1.2.1, 1.2.2, 1.2.4, 2.0.0, 2.2.0, 2.3.0, 2.5.0</t>
+  </si>
+  <si>
+    <t>0.45.1, 0.46.2</t>
+  </si>
+  <si>
+    <t>0.45.0, 0.45.1</t>
+  </si>
+  <si>
+    <t>0.45.0, 0.45.1, 0.45.2, 0.45.3, 0.46.0, 0.46.1, 0.46.2, 0.46.3, 1.0.0, 1.0.1, 1.0.2, 1.1.0, 1.1.1, 1.1.2, 1.2.0, 1.2.1, 1.2.2, 1.2.4, 2.0.0</t>
+  </si>
+  <si>
+    <t>Case_number</t>
+  </si>
+  <si>
+    <t>Versions</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -45,16 +116,316 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -62,14 +433,206 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="8"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="강조색1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="강조색2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="강조색3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="강조색4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="강조색5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="강조색6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="경고문" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="계산" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="나쁨" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="메모" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="보통" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="설명 텍스트" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="셀 확인" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="연결된 셀" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="요약" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="입력" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="제목" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="제목 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="제목 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="제목 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="제목 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -402,9 +965,1874 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8E766C3-C370-435D-83DA-FB2505DB5306}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C169"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+    <col min="2" max="2" width="69.140625" customWidth="1"/>
+    <col min="3" max="3" width="155.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>30</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>32</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>32</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>34</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>36</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>42</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>47</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>48</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>58</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>61</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>66</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>68</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>72</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>92</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>96</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>98</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>99</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>1005</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>1013</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>1020</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>1035</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>1054</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>1059</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>1066</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>118</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>131</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>133</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>137</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>140</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>143</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>146</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>155</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>157</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>172</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <v>174</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>177</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <v>181</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
+        <v>189</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>210</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
+        <v>225</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>226</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <v>233</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
+        <v>240</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
+        <v>242</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>249</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <v>257</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
+        <v>261</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
+        <v>264</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
+        <v>280</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
+        <v>289</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
+        <v>295</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
+        <v>297</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
+        <v>302</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
+        <v>304</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
+        <v>309</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
+        <v>315</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
+        <v>317</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
+        <v>322</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
+        <v>327</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
+        <v>336</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
+        <v>344</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
+        <v>348</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
+        <v>362</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
+        <v>369</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
+        <v>380</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
+        <v>382</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
+        <v>396</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
+        <v>403</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
+        <v>415</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
+        <v>417</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
+        <v>436</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
+        <v>443</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="3">
+        <v>453</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="3">
+        <v>454</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="3">
+        <v>464</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
+        <v>467</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="3">
+        <v>468</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
+        <v>475</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
+        <v>487</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="3">
+        <v>497</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
+        <v>504</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="3">
+        <v>505</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="3">
+        <v>507</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
+        <v>523</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="3">
+        <v>535</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3">
+        <v>548</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="3">
+        <v>553</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="3">
+        <v>559</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="3">
+        <v>561</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="3">
+        <v>565</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="3">
+        <v>568</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="3">
+        <v>571</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="3">
+        <v>578</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="3">
+        <v>595</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="3">
+        <v>596</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="3">
+        <v>600</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="3">
+        <v>621</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="3">
+        <v>622</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="3">
+        <v>624</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="3">
+        <v>634</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="3">
+        <v>635</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="3">
+        <v>637</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="3">
+        <v>662</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="3">
+        <v>663</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="3">
+        <v>671</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="3">
+        <v>674</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="3">
+        <v>696</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="3">
+        <v>727</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="3">
+        <v>734</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="3">
+        <v>742</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="3">
+        <v>747</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="3">
+        <v>750</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="3">
+        <v>751</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="3">
+        <v>764</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="3">
+        <v>769</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="3">
+        <v>772</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="3">
+        <v>773</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="3">
+        <v>775</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="3">
+        <v>777</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="3">
+        <v>781</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="3">
+        <v>789</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="3">
+        <v>790</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="3">
+        <v>795</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="3">
+        <v>800</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="3">
+        <v>803</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="3">
+        <v>810</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="3">
+        <v>812</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="3">
+        <v>816</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="3">
+        <v>822</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="3">
+        <v>825</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="3">
+        <v>827</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="3">
+        <v>843</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="3">
+        <v>855</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="3">
+        <v>858</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="3">
+        <v>861</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="3">
+        <v>876</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="3">
+        <v>877</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="3">
+        <v>886</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="3">
+        <v>889</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="3">
+        <v>901</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="3">
+        <v>911</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="3">
+        <v>917</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="3">
+        <v>921</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="3">
+        <v>925</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="3">
+        <v>927</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="3">
+        <v>933</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="3">
+        <v>941</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="3">
+        <v>944</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="3">
+        <v>950</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="3">
+        <v>958</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="3">
+        <v>961</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="3">
+        <v>969</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="3">
+        <v>977</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="3">
+        <v>979</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="3">
+        <v>985</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="3">
+        <v>988</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="3">
+        <v>989</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="3">
+        <v>994</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>